--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M561"/>
+  <dimension ref="A1:M566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25691,6 +25691,231 @@
       <c r="M561" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:12:44+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>395.91</v>
+      </c>
+      <c r="C562" t="n">
+        <v>398.26</v>
+      </c>
+      <c r="D562" t="n">
+        <v>396.72</v>
+      </c>
+      <c r="E562" t="n">
+        <v>395.28</v>
+      </c>
+      <c r="F562" t="n">
+        <v>392.12</v>
+      </c>
+      <c r="G562" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="H562" t="n">
+        <v>390.07</v>
+      </c>
+      <c r="I562" t="n">
+        <v>388.35</v>
+      </c>
+      <c r="J562" t="n">
+        <v>382.77</v>
+      </c>
+      <c r="K562" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="L562" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>395.93</v>
+      </c>
+      <c r="C563" t="n">
+        <v>397.69</v>
+      </c>
+      <c r="D563" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="E563" t="n">
+        <v>395.06</v>
+      </c>
+      <c r="F563" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="G563" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="H563" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="I563" t="n">
+        <v>389.16</v>
+      </c>
+      <c r="J563" t="n">
+        <v>384</v>
+      </c>
+      <c r="K563" t="n">
+        <v>372.32</v>
+      </c>
+      <c r="L563" t="n">
+        <v>373.01</v>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>395.93</v>
+      </c>
+      <c r="C564" t="n">
+        <v>397.69</v>
+      </c>
+      <c r="D564" t="n">
+        <v>396.19</v>
+      </c>
+      <c r="E564" t="n">
+        <v>395.06</v>
+      </c>
+      <c r="F564" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="G564" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="H564" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="I564" t="n">
+        <v>389.16</v>
+      </c>
+      <c r="J564" t="n">
+        <v>384</v>
+      </c>
+      <c r="K564" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="L564" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>395.82</v>
+      </c>
+      <c r="C565" t="n">
+        <v>397.98</v>
+      </c>
+      <c r="D565" t="n">
+        <v>396.08</v>
+      </c>
+      <c r="E565" t="n">
+        <v>394.71</v>
+      </c>
+      <c r="F565" t="n">
+        <v>392.56</v>
+      </c>
+      <c r="G565" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="H565" t="n">
+        <v>389.6</v>
+      </c>
+      <c r="I565" t="n">
+        <v>387.63</v>
+      </c>
+      <c r="J565" t="n">
+        <v>382.77</v>
+      </c>
+      <c r="K565" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="L565" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:20+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>395.62</v>
+      </c>
+      <c r="C566" t="n">
+        <v>397.36</v>
+      </c>
+      <c r="D566" t="n">
+        <v>395.66</v>
+      </c>
+      <c r="E566" t="n">
+        <v>394.23</v>
+      </c>
+      <c r="F566" t="n">
+        <v>391.68</v>
+      </c>
+      <c r="G566" t="n">
+        <v>385.84</v>
+      </c>
+      <c r="H566" t="n">
+        <v>389.32</v>
+      </c>
+      <c r="I566" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="J566" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="K566" t="n">
+        <v>370.87</v>
+      </c>
+      <c r="L566" t="n">
+        <v>372.24</v>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -25705,7 +25930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B583"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31538,6 +31763,56 @@
       </c>
       <c r="B583" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -31706,28 +31981,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1002347860627169</v>
+        <v>-0.1046368728339556</v>
       </c>
       <c r="J2" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K2" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009897467817380101</v>
+        <v>0.01098599187673277</v>
       </c>
       <c r="M2" t="n">
-        <v>6.291725085739076</v>
+        <v>6.260322236665242</v>
       </c>
       <c r="N2" t="n">
-        <v>58.28398544025447</v>
+        <v>57.82337088983166</v>
       </c>
       <c r="O2" t="n">
-        <v>7.634394896797943</v>
+        <v>7.604167994582423</v>
       </c>
       <c r="P2" t="n">
-        <v>401.0678853685436</v>
+        <v>401.1130380947821</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31784,28 +32059,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07604183546879263</v>
+        <v>-0.078213688763571</v>
       </c>
       <c r="J3" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K3" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006768647925709415</v>
+        <v>0.007302594393904793</v>
       </c>
       <c r="M3" t="n">
-        <v>5.451011013315525</v>
+        <v>5.414205585445277</v>
       </c>
       <c r="N3" t="n">
-        <v>49.20507635992553</v>
+        <v>48.78383946583575</v>
       </c>
       <c r="O3" t="n">
-        <v>7.014633016767558</v>
+        <v>6.984542895983656</v>
       </c>
       <c r="P3" t="n">
-        <v>401.0875771922014</v>
+        <v>401.1098578865257</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31862,28 +32137,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03601650682800146</v>
+        <v>-0.03734854892089092</v>
       </c>
       <c r="J4" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K4" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002300900246314685</v>
+        <v>0.00252425476456597</v>
       </c>
       <c r="M4" t="n">
-        <v>4.644717529968549</v>
+        <v>4.609859687459041</v>
       </c>
       <c r="N4" t="n">
-        <v>32.62428813537903</v>
+        <v>32.3411002393802</v>
       </c>
       <c r="O4" t="n">
-        <v>5.711767514121966</v>
+        <v>5.68692361821224</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9019706065587</v>
+        <v>397.9156487116939</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31940,28 +32215,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01307367848642554</v>
+        <v>-0.01335028175193544</v>
       </c>
       <c r="J5" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K5" t="n">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003095798802651428</v>
+        <v>0.0003294576017240924</v>
       </c>
       <c r="M5" t="n">
-        <v>4.593205305754969</v>
+        <v>4.555030661534803</v>
       </c>
       <c r="N5" t="n">
-        <v>32.01286029094521</v>
+        <v>31.73046157354024</v>
       </c>
       <c r="O5" t="n">
-        <v>5.657990835176848</v>
+        <v>5.63297981298888</v>
       </c>
       <c r="P5" t="n">
-        <v>395.3773366953874</v>
+        <v>395.3801835464774</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32018,28 +32293,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09880380284433275</v>
+        <v>-0.09935802562546492</v>
       </c>
       <c r="J6" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K6" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02161616627182039</v>
+        <v>0.0222937447831828</v>
       </c>
       <c r="M6" t="n">
-        <v>4.213771264764005</v>
+        <v>4.179380212497066</v>
       </c>
       <c r="N6" t="n">
-        <v>25.62324617616073</v>
+        <v>25.39814552482968</v>
       </c>
       <c r="O6" t="n">
-        <v>5.061940949493655</v>
+        <v>5.039657282477616</v>
       </c>
       <c r="P6" t="n">
-        <v>395.179144197605</v>
+        <v>395.184830665711</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32096,28 +32371,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03333261977977148</v>
+        <v>-0.04421384413991128</v>
       </c>
       <c r="J7" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K7" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002442664954475648</v>
+        <v>0.00432209367623082</v>
       </c>
       <c r="M7" t="n">
-        <v>3.982780066251936</v>
+        <v>3.998802243855158</v>
       </c>
       <c r="N7" t="n">
-        <v>26.31292295982699</v>
+        <v>26.41873262916014</v>
       </c>
       <c r="O7" t="n">
-        <v>5.129612359606424</v>
+        <v>5.139915624712154</v>
       </c>
       <c r="P7" t="n">
-        <v>393.2977486757796</v>
+        <v>393.4093486566445</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32174,28 +32449,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08859093232361981</v>
+        <v>0.08794970172479651</v>
       </c>
       <c r="J8" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K8" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01464699541016545</v>
+        <v>0.01473102278208549</v>
       </c>
       <c r="M8" t="n">
-        <v>4.277154696806444</v>
+        <v>4.243737680026441</v>
       </c>
       <c r="N8" t="n">
-        <v>30.61808868513572</v>
+        <v>30.35018774518099</v>
       </c>
       <c r="O8" t="n">
-        <v>5.533361427300382</v>
+        <v>5.509100447911709</v>
       </c>
       <c r="P8" t="n">
-        <v>387.9714631395157</v>
+        <v>387.9780479238343</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32252,28 +32527,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07257979792297944</v>
+        <v>0.07401808274737286</v>
       </c>
       <c r="J9" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K9" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009018054640032358</v>
+        <v>0.009563949641693381</v>
       </c>
       <c r="M9" t="n">
-        <v>4.725883182967833</v>
+        <v>4.692667380992519</v>
       </c>
       <c r="N9" t="n">
-        <v>33.56917141805803</v>
+        <v>33.2840031813729</v>
       </c>
       <c r="O9" t="n">
-        <v>5.793890870395992</v>
+        <v>5.769228993667429</v>
       </c>
       <c r="P9" t="n">
-        <v>385.4983393817018</v>
+        <v>385.4836009214523</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32330,28 +32605,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08629060875187676</v>
+        <v>-0.08396849105164143</v>
       </c>
       <c r="J10" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K10" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01150436083243045</v>
+        <v>0.01111722166492057</v>
       </c>
       <c r="M10" t="n">
-        <v>4.895103447555997</v>
+        <v>4.862586363006584</v>
       </c>
       <c r="N10" t="n">
-        <v>37.10184963953333</v>
+        <v>36.79187989666011</v>
       </c>
       <c r="O10" t="n">
-        <v>6.091128765633948</v>
+        <v>6.065631038619157</v>
       </c>
       <c r="P10" t="n">
-        <v>384.2691032587136</v>
+        <v>384.2452895740307</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32408,28 +32683,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08939830602952201</v>
+        <v>-0.1000474078276058</v>
       </c>
       <c r="J11" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K11" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01258869563002418</v>
+        <v>0.01589476308930071</v>
       </c>
       <c r="M11" t="n">
-        <v>4.645837372032635</v>
+        <v>4.663929741354732</v>
       </c>
       <c r="N11" t="n">
-        <v>36.35232340846222</v>
+        <v>36.35548126228307</v>
       </c>
       <c r="O11" t="n">
-        <v>6.029288797898325</v>
+        <v>6.029550668356895</v>
       </c>
       <c r="P11" t="n">
-        <v>380.0452207301719</v>
+        <v>380.1544500190231</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32486,28 +32761,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08728791563602481</v>
+        <v>-0.09457621788325223</v>
       </c>
       <c r="J12" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="K12" t="n">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008315438951810861</v>
+        <v>0.009917914405229822</v>
       </c>
       <c r="M12" t="n">
-        <v>5.64802971855338</v>
+        <v>5.631989391490597</v>
       </c>
       <c r="N12" t="n">
-        <v>52.69299100649397</v>
+        <v>52.3824086678293</v>
       </c>
       <c r="O12" t="n">
-        <v>7.258993801243666</v>
+        <v>7.237569251332197</v>
       </c>
       <c r="P12" t="n">
-        <v>379.247484692495</v>
+        <v>379.3222342432161</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32545,7 +32820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M561"/>
+  <dimension ref="A1:M566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70127,6 +70402,341 @@
         </is>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:12:44+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-42.05965424323505,171.36381058257285</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-42.05898808656497,171.3638689099774</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-42.058325738670696,171.3639739612846</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-42.05766328572087,171.36407781110984</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-42.057002512908106,171.3642023193117</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-42.05634527399185,171.36437018561418</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-42.055676758040974,171.3644000479234</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-42.05501455185829,171.36450725916137</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-42.054356124715675,171.36466083011743</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-42.05370361460393,171.3648869417986</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-42.053039229615784,171.3649677277221</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:18:58+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-42.05965422361688,171.3638103423452</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-42.05898864567975,171.3638757563957</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-42.05832625854419,171.36398032718722</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-42.05766350151534,171.36408045353286</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-42.05700229711616,171.36419967691558</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-42.056344263709455,171.36435781452076</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-42.055676365699206,171.36439524366548</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-42.05501375737411,171.36449753063874</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-42.054354918294614,171.3646460573251</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-42.05370246705888,171.36487288976943</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-42.05303787611089,171.36495115370488</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-42.05965422361688,171.3638103423452</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-42.05898864567975,171.3638757563957</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-42.05832625854419,171.36398032718722</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-42.05766350151534,171.36408045353286</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-42.05700229711616,171.36419967691558</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-42.056344263709455,171.36435781452076</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-42.055676365699206,171.36439524366548</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-42.05501375737411,171.36449753063874</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-42.054354918294614,171.3646460573251</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-42.05370276130136,171.3648764928538</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-42.05303711108534,171.3649417857824</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-42.05965433151679,171.3638116635975</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-42.0589883612179,171.36387227313023</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-42.05832636644242,171.3639816484123</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-42.05766384482462,171.36408465738776</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-42.05700208132416,171.36419703451952</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-42.05634387136642,171.36435301021277</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-42.055677219042266,171.3644056929265</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-42.05501525806576,171.36451590673727</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-42.054356124715675,171.36466083011743</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-42.0537035263313,171.36488586087327</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-42.05303800361509,171.3649527150253</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:20+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-42.05965452769843,171.36381406587444</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-42.05898896937759,171.36387972011158</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-42.05832677841735,171.36398669308997</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-42.057664315648495,171.36409042267456</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-42.05700294449181,171.36420760410397</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-42.05634479337223,171.3643643003367</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-42.055677493681216,171.36440905590717</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-42.05501577791251,171.36452227231408</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-42.054356007016146,171.36465938886934</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>-42.053703889229844,171.36489030467746</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>-42.053038631327695,171.36496040152596</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0380/nzd0380.xlsx
+++ b/data/nzd0380/nzd0380.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M566"/>
+  <dimension ref="A1:M569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25916,6 +25916,141 @@
       <c r="M566" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="C567" t="n">
+        <v>397.37</v>
+      </c>
+      <c r="D567" t="n">
+        <v>395.79</v>
+      </c>
+      <c r="E567" t="n">
+        <v>394.32</v>
+      </c>
+      <c r="F567" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="G567" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="H567" t="n">
+        <v>389.31</v>
+      </c>
+      <c r="I567" t="n">
+        <v>387.02</v>
+      </c>
+      <c r="J567" t="n">
+        <v>383.59</v>
+      </c>
+      <c r="K567" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="L567" t="n">
+        <v>372.86</v>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:13:05+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>393.61</v>
+      </c>
+      <c r="C568" t="n">
+        <v>394.54</v>
+      </c>
+      <c r="D568" t="n">
+        <v>392.44</v>
+      </c>
+      <c r="E568" t="n">
+        <v>391.81</v>
+      </c>
+      <c r="F568" t="n">
+        <v>389.43</v>
+      </c>
+      <c r="G568" t="n">
+        <v>383.24</v>
+      </c>
+      <c r="H568" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="I568" t="n">
+        <v>386.58</v>
+      </c>
+      <c r="J568" t="n">
+        <v>384.74</v>
+      </c>
+      <c r="K568" t="n">
+        <v>370.71</v>
+      </c>
+      <c r="L568" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:19:20+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>393.83</v>
+      </c>
+      <c r="C569" t="n">
+        <v>394.68</v>
+      </c>
+      <c r="D569" t="n">
+        <v>393.32</v>
+      </c>
+      <c r="E569" t="n">
+        <v>392.72</v>
+      </c>
+      <c r="F569" t="n">
+        <v>390.52</v>
+      </c>
+      <c r="G569" t="n">
+        <v>384.37</v>
+      </c>
+      <c r="H569" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="I569" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="J569" t="n">
+        <v>384.59</v>
+      </c>
+      <c r="K569" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="L569" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25930,7 +26065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B588"/>
+  <dimension ref="A1:B591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31813,6 +31948,36 @@
       </c>
       <c r="B588" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -31981,28 +32146,28 @@
         <v>0.0545</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1046368728339556</v>
+        <v>-0.108746975975778</v>
       </c>
       <c r="J2" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K2" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01098599187673277</v>
+        <v>0.01198000769102192</v>
       </c>
       <c r="M2" t="n">
-        <v>6.260322236665242</v>
+        <v>6.249711761578534</v>
       </c>
       <c r="N2" t="n">
-        <v>57.82337088983166</v>
+        <v>57.60386616117669</v>
       </c>
       <c r="O2" t="n">
-        <v>7.604167994582423</v>
+        <v>7.589721085861897</v>
       </c>
       <c r="P2" t="n">
-        <v>401.1130380947821</v>
+        <v>401.1553482137118</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32059,28 +32224,28 @@
         <v>0.0592</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.078213688763571</v>
+        <v>-0.08180248081085047</v>
       </c>
       <c r="J3" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K3" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007302594393904793</v>
+        <v>0.008066929409997869</v>
       </c>
       <c r="M3" t="n">
-        <v>5.414205585445277</v>
+        <v>5.404335703164215</v>
       </c>
       <c r="N3" t="n">
-        <v>48.78383946583575</v>
+        <v>48.59769615636874</v>
       </c>
       <c r="O3" t="n">
-        <v>6.984542895983656</v>
+        <v>6.971204785140711</v>
       </c>
       <c r="P3" t="n">
-        <v>401.1098578865257</v>
+        <v>401.1468081477648</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32137,28 +32302,28 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03734854892089092</v>
+        <v>-0.04051289213487556</v>
       </c>
       <c r="J4" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K4" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00252425476456597</v>
+        <v>0.002999165741129239</v>
       </c>
       <c r="M4" t="n">
-        <v>4.609859687459041</v>
+        <v>4.600429704409134</v>
       </c>
       <c r="N4" t="n">
-        <v>32.3411002393802</v>
+        <v>32.22925525266515</v>
       </c>
       <c r="O4" t="n">
-        <v>5.68692361821224</v>
+        <v>5.67708157882773</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9156487116939</v>
+        <v>397.9482510044973</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32215,28 +32380,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01335028175193544</v>
+        <v>-0.01549019585954507</v>
       </c>
       <c r="J5" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K5" t="n">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0003294576017240924</v>
+        <v>0.0004484671282766195</v>
       </c>
       <c r="M5" t="n">
-        <v>4.555030661534803</v>
+        <v>4.541731119559324</v>
       </c>
       <c r="N5" t="n">
-        <v>31.73046157354024</v>
+        <v>31.59054449383848</v>
       </c>
       <c r="O5" t="n">
-        <v>5.63297981298888</v>
+        <v>5.620546636568234</v>
       </c>
       <c r="P5" t="n">
-        <v>395.3801835464774</v>
+        <v>395.4022311922157</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32293,28 +32458,28 @@
         <v>0.078</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09935802562546492</v>
+        <v>-0.1014506976761159</v>
       </c>
       <c r="J6" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K6" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0222937447831828</v>
+        <v>0.0234731579045494</v>
       </c>
       <c r="M6" t="n">
-        <v>4.179380212497066</v>
+        <v>4.167655408753959</v>
       </c>
       <c r="N6" t="n">
-        <v>25.39814552482968</v>
+        <v>25.28898275018922</v>
       </c>
       <c r="O6" t="n">
-        <v>5.039657282477616</v>
+        <v>5.028815243194884</v>
       </c>
       <c r="P6" t="n">
-        <v>395.184830665711</v>
+        <v>395.2063747993887</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32371,28 +32536,28 @@
         <v>0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04421384413991128</v>
+        <v>-0.05226626606886135</v>
       </c>
       <c r="J7" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K7" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00432209367623082</v>
+        <v>0.00602901130942779</v>
       </c>
       <c r="M7" t="n">
-        <v>3.998802243855158</v>
+        <v>4.01543789673469</v>
       </c>
       <c r="N7" t="n">
-        <v>26.41873262916014</v>
+        <v>26.59984948407681</v>
       </c>
       <c r="O7" t="n">
-        <v>5.139915624712154</v>
+        <v>5.157504191377532</v>
       </c>
       <c r="P7" t="n">
-        <v>393.4093486566445</v>
+        <v>393.4922318364031</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32449,28 +32614,28 @@
         <v>0.0575</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08794970172479651</v>
+        <v>0.08624598410682925</v>
       </c>
       <c r="J8" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K8" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01473102278208549</v>
+        <v>0.01433621854973044</v>
       </c>
       <c r="M8" t="n">
-        <v>4.243737680026441</v>
+        <v>4.230829895515924</v>
       </c>
       <c r="N8" t="n">
-        <v>30.35018774518099</v>
+        <v>30.20512022685569</v>
       </c>
       <c r="O8" t="n">
-        <v>5.509100447911709</v>
+        <v>5.495918506205827</v>
       </c>
       <c r="P8" t="n">
-        <v>387.9780479238343</v>
+        <v>387.9955868023514</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32527,28 +32692,28 @@
         <v>0.043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07401808274737286</v>
+        <v>0.07331818782168747</v>
       </c>
       <c r="J9" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K9" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009563949641693381</v>
+        <v>0.009497698063254623</v>
       </c>
       <c r="M9" t="n">
-        <v>4.692667380992519</v>
+        <v>4.671390899189041</v>
       </c>
       <c r="N9" t="n">
-        <v>33.2840031813729</v>
+        <v>33.11076336503578</v>
       </c>
       <c r="O9" t="n">
-        <v>5.769228993667429</v>
+        <v>5.754195283880778</v>
       </c>
       <c r="P9" t="n">
-        <v>385.4836009214523</v>
+        <v>385.4908056423192</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32605,28 +32770,28 @@
         <v>0.0397</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08396849105164143</v>
+        <v>-0.08156338406506614</v>
       </c>
       <c r="J10" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K10" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01111722166492057</v>
+        <v>0.01061360328362437</v>
       </c>
       <c r="M10" t="n">
-        <v>4.862586363006584</v>
+        <v>4.848048190933453</v>
       </c>
       <c r="N10" t="n">
-        <v>36.79187989666011</v>
+        <v>36.62706980530886</v>
       </c>
       <c r="O10" t="n">
-        <v>6.065631038619157</v>
+        <v>6.052030221777553</v>
       </c>
       <c r="P10" t="n">
-        <v>384.2452895740307</v>
+        <v>384.2205308146933</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32683,28 +32848,28 @@
         <v>0.0494</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1000474078276058</v>
+        <v>-0.1069070057937471</v>
       </c>
       <c r="J11" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K11" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01589476308930071</v>
+        <v>0.01821057713450103</v>
       </c>
       <c r="M11" t="n">
-        <v>4.663929741354732</v>
+        <v>4.677452149797189</v>
       </c>
       <c r="N11" t="n">
-        <v>36.35548126228307</v>
+        <v>36.39281004546168</v>
       </c>
       <c r="O11" t="n">
-        <v>6.029550668356895</v>
+        <v>6.032645360491671</v>
       </c>
       <c r="P11" t="n">
-        <v>380.1544500190231</v>
+        <v>380.2250514178371</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32761,28 +32926,28 @@
         <v>0.0491</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09457621788325223</v>
+        <v>-0.09991475185289146</v>
       </c>
       <c r="J12" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="K12" t="n">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009917914405229822</v>
+        <v>0.0111588680464132</v>
       </c>
       <c r="M12" t="n">
-        <v>5.631989391490597</v>
+        <v>5.627420791054702</v>
       </c>
       <c r="N12" t="n">
-        <v>52.3824086678293</v>
+        <v>52.24854829792277</v>
       </c>
       <c r="O12" t="n">
-        <v>7.237569251332197</v>
+        <v>7.228315730370579</v>
       </c>
       <c r="P12" t="n">
-        <v>379.3222342432161</v>
+        <v>379.3771885108804</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32820,7 +32985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M566"/>
+  <dimension ref="A1:M569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70737,6 +70902,207 @@
         </is>
       </c>
     </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:12:59+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-42.05965464540737,171.36381550724064</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-42.058988959568566,171.363879599999</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-42.05832665090132,171.3639851316421</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-42.05766422736904,171.3640893416833</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-42.057003130857424,171.36420988617337</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-42.0563449699264,171.36436646227534</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-42.05567750348975,171.36440917601362</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-42.05501585637992,171.36452323315586</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-42.054355320435185,171.36465098158914</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>-42.05370359498779,171.36488670159298</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>-42.0530380232311,171.36495295522843</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:13:05+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-42.05965649932097,171.36383820875872</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-42.05899173551726,171.3639135918675</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-42.05832993688441,171.36402536895443</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-42.05766668938121,171.36411948933028</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-42.05700515145016,171.36423462861114</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-42.05634734359532,171.36439552834088</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-42.055678592236006,171.36442250783003</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-42.0550162879505,171.36452851778577</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-42.054354192479416,171.36463716962922</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>-42.05370404615889,171.36489222632252</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>-42.05303972982352,171.36497385290258</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:19:20+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-42.05965628352174,171.3638355662539</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-42.058991598191405,171.36391191029088</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-42.05832907370215,171.36401479915256</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-42.05766579678009,171.36410855930657</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-42.057004082302235,171.3642215367385</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-42.056346235230166,171.36438195616947</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-42.0556781998952,171.3644177035718</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-42.055016062356806,171.36452575536558</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-42.05435433960418,171.36463897118918</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>-42.05370418347178,171.36489390776197</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>-42.05304000444723,171.36497721574682</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
